--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Material.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Material.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>matéria escura</t>
+          <t>matéria sombria</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「Carvalho」</t>
+          <t>carvalho</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Floresta, Madeira</t>
+          <t>floresta,madeira</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「Ferro」</t>
+          <t>ferro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Massa</t>
+          <t>massa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「Granito」</t>
+          <t>granito</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rígido, Pedra</t>
+          <t>rígido,pedra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「Lama」</t>
+          <t>lama</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「Grama」</t>
+          <t>grama</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prática</t>
+          <t>treino</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「Grama da Floresta」</t>
+          <t>grama da floresta</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「Grama Profunda」</t>
+          <t>grama alta</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「Areia」</t>
+          <t>areia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brinquedo</t>
+          <t>brinquedo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「Geleia」</t>
+          <t>geleia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tremor</t>
+          <t>trêmula</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「Comida Crua」</t>
+          <t>comida crua</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Comestível</t>
+          <t>comestível</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「Acácia」</t>
+          <t>acácia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「Ouro」</t>
+          <t>ouro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dourado</t>
+          <t>dourado</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「Prata」</t>
+          <t>prata</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Medo da Morte</t>
+          <t>pavor</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「Cobre」</t>
+          <t>cobre</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Relâmpago</t>
+          <t>relâmpago</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「Bronze」</t>
+          <t>bronze</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nobra</t>
+          <t>nobre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「Mica」</t>
+          <t>mica</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Efêmero</t>
+          <t>efêmero</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「Cromita」</t>
+          <t>cromita</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Puro</t>
+          <t>revelador</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「Rubínus」</t>
+          <t>rubynus</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Carmesim</t>
+          <t>carmesim</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「Aço」</t>
+          <t>aço</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Histórico</t>
+          <t>histórico</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「Coral」</t>
+          <t>coral</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oceano</t>
+          <t>oceânico</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「Areia de Quartzo」</t>
+          <t>areia de quartzo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cintilante, Vidro</t>
+          <t>cintilante,vidro</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「Cristal」</t>
+          <t>cristal</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luminescente</t>
+          <t>luminescente</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「Pele」</t>
+          <t>couro cru</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Misterioso</t>
+          <t>misterioso</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「Escama de Dragão」</t>
+          <t>escama de dragão</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Matador de Dragões</t>
+          <t>dracônico</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「Pérola」</t>
+          <t>pérola</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brilhante</t>
+          <t>brilhante</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「Esmeralda」</t>
+          <t>esmeralda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Milagre</t>
+          <t>milagroso</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「Cobalto」</t>
+          <t>cobalto</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「Adamantite」</t>
+          <t>adamantita</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Terremoto</t>
+          <t>sísmico</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「Safira」</t>
+          <t>safira</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「Topázio」</t>
+          <t>topázio</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「Água-Marinha」</t>
+          <t>água-marinha</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「Opal」</t>
+          <t>opala</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「Jade」</t>
+          <t>jade</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「Ônyx」</t>
+          <t>ônix</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「Lápis-Lazúli」</t>
+          <t>lápis-lazúli</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「Turquesa」</t>
+          <t>turquesa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「Meteorito」</t>
+          <t>meteorito</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「Platina」</t>
+          <t>platina</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brilhante</t>
+          <t>deslumbrante</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「Osso」</t>
+          <t>osso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Imortal</t>
+          <t>imortal</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「Bétula」</t>
+          <t>bétula</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「Papel」</t>
+          <t>papel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bobo</t>
+          <t>bobo</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>「Éter」</t>
+          <t>éter</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Eterno</t>
+          <t>eterno</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「Pinheiro」</t>
+          <t>pinheiro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「Solo」</t>
+          <t>terra</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「Solo de Floresta」</t>
+          <t>terra da floresta</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「Solo Profundo」</t>
+          <t>terra profunda</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「Neve」</t>
+          <t>neve</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>「Calcário」</t>
+          <t>calcário</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「Mármore」</t>
+          <t>mármore</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「Basalto」</t>
+          <t>basalto</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「Ardósia」</t>
+          <t>ardósia</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「Silte」</t>
+          <t>lodo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「Diorito」</t>
+          <t>diorito</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「Obsidiana」</t>
+          <t>obsidiana</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Matador de Deuses</t>
+          <t>maldição divina</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「Filito」</t>
+          <t>filito</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「Água Termal」</t>
+          <t>água de fonte termal</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「Solo Leve」</t>
+          <t>terra pálida</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「Mogno」</t>
+          <t>mogno</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「Roseira」</t>
+          <t>pau-rosa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「Gelo」</t>
+          <t>gelo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「Palha」</t>
+          <t>palha</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trabalho na Fazenda</t>
+          <t>lavoura</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「Cedro」</t>
+          <t>cedro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「Solo Místico」</t>
+          <t>terra mística</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「Grama Mística」</t>
+          <t>grama mística</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>「Água」</t>
+          <t>água</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>「Água Doce」</t>
+          <t>água doce</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「Mithril」</t>
+          <t>mithril</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Antigo</t>
+          <t>ancestral</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>「Titânio」</t>
+          <t>titânio</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Intacto</t>
+          <t>inoxidável</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>「Algodão」</t>
+          <t>algodão</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leve</t>
+          <t>leve</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>「Seda」</t>
+          <t>seda</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Belo</t>
+          <t>belo</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>「Escama」</t>
+          <t>escama</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ira</t>
+          <t>fúria</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>「Caxemira」</t>
+          <t>cashmere</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Quente</t>
+          <t>morno</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>「Zylon」</t>
+          <t>zylon</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Exótico</t>
+          <t>exótico</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>「Tecido Espiritual」</t>
+          <t>tecido espiritual</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>De Outro Mundo</t>
+          <t>de outro mundo</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>「Tecido da Aurora」</t>
+          <t>tecido do alvorecer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Crepúsculo</t>
+          <t>crepuscular</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>「Escama de Grifo」</t>
+          <t>escama de grifo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Caído</t>
+          <t>caído</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>「Plástico」</t>
+          <t>plástico</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Transparente</t>
+          <t>transparente</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>「Solo Azul」</t>
+          <t>terra azul</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>「Lã」</t>
+          <t>lã</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Suave</t>
+          <t>macio</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>「Seda de Aranha」</t>
+          <t>seda de aranha</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Emaranhado</t>
+          <t>enredado</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>「Cinza」</t>
+          <t>cinza</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>「Solo Vermelho」</t>
+          <t>terra vermelha</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>「Abeto」</t>
+          <t>abeto</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>「Palulu」</t>
+          <t>palulu</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>「Solo Leve」</t>
+          <t>terra leve</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>「Solo Amarelo」</t>
+          <t>terra amarela</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>「Água do Mar」</t>
+          <t>água do mar</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>「Água Tropical」</t>
+          <t>água tropical</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>「Areia Branca」</t>
+          <t>areia branca</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>「Cânhamo」</t>
+          <t>cânhamo</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Resistente</t>
+          <t>resistente</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>「Salgueiro」</t>
+          <t>salgueiro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>「Flor de Cerejeira」</t>
+          <t>flor de cerejeira</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>「Comida Processada」</t>
+          <t>comida processada</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>「Carbono」</t>
+          <t>carbono</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>「Álamo」</t>
+          <t>álamo</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>「Areia do Mar」</t>
+          <t>areia do mar</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「Bambu」</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>「Ametista」</t>
+          <t>ametista</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Encantadora</t>
+          <t>fascinante</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>「Madeira Feérica」</t>
+          <t>madeira feérica</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>「Madeira de Coral」</t>
+          <t>madeira de coral</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>「Quartzo Rosa」</t>
+          <t>quartzo-rosa</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Adorável</t>
+          <t>adorável</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>「Creme Fresco」</t>
+          <t>creme fresco</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>「Âmbar」</t>
+          <t>âmbar</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>「Magma」</t>
+          <t>magma</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>「Sangue」</t>
+          <t>sangue</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>「Obsidiana Verdadeira」</t>
+          <t>obsidiana verdadeira</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>antinômico</t>
+          <t xml:space="preserve">fora da lei </t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ouro ancestral</t>
+          <t>ouro ancião</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>crepúsculo</t>
+          <t>crepuscular</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>「Oricalco」</t>
+          <t>oricalco</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>「Aço Profundo」</t>
+          <t>aço profundo</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>「Netherita」</t>
+          <t>netherita</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>purgatório</t>
+          <t xml:space="preserve">infernal </t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>「Areia Eterna」</t>
+          <t>areia eterna</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>infinito</t>
+          <t>infinita</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>「Ferro Imperecível」</t>
+          <t>ferro imperecível</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>eterno</t>
+          <t>imperecível</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4377,6 +4377,48 @@
       <c r="H116" t="inlineStr">
         <is>
           <t>うつろわざる</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EA 23.283</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>nuvem</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>雲</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>fofa</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>puffy</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>ふわふわの</t>
         </is>
       </c>
     </row>
